--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484104_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484104_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6412</v>
+        <v>3.7098</v>
       </c>
       <c r="E2" t="n">
-        <v>2.093</v>
+        <v>2.2177</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5482</v>
+        <v>1.4921</v>
       </c>
       <c r="G2" t="n">
         <v>3.4325</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3945</v>
+        <v>-0.3259</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3797</v>
+        <v>-0.255</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0149</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.6032</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MONTALVO PEREZ</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1714</v>
+        <v>2.7266</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1618</v>
+        <v>1.9175</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3332</v>
+        <v>0.8091</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5443</v>
+        <v>0.5598</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.8218</v>
+        <v>-1.285</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2775</v>
+        <v>1.8449</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5357</v>
+        <v>1.511</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.5839</v>
+        <v>-0.3014</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0482</v>
+        <v>1.8124</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0086</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2379</v>
+        <v>-0.9837</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.0325</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9758</v>
+        <v>1.1903</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9677</v>
+        <v>3.3725</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0059</v>
+        <v>-1.1705</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0998</v>
+        <v>0.1758</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9061</v>
+        <v>-1.3463</v>
       </c>
       <c r="V3" t="n">
+        <v>2.1469</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.4129</v>
+      </c>
+      <c r="X3" t="n">
         <v>-0.266</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.532</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>A. MONTALVO PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4336</v>
+        <v>1.4786</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7928</v>
+        <v>-1.0971</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6408</v>
+        <v>2.5757</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5598</v>
+        <v>-1.5443</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.285</v>
+        <v>-2.8218</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8449</v>
+        <v>1.2775</v>
       </c>
       <c r="J4" t="n">
-        <v>1.511</v>
+        <v>-0.5357</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3014</v>
+        <v>-2.5839</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8124</v>
+        <v>2.0482</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-1.0086</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9837</v>
+        <v>-0.2379</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0325</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1903</v>
+        <v>2.9758</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3725</v>
+        <v>3.9677</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4635</v>
+        <v>0.3131</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0511</v>
+        <v>0.1645</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.5146</v>
+        <v>0.1486</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1469</v>
+        <v>-0.266</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4129</v>
+        <v>0.266</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2004</v>
+        <v>1.372</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1622</v>
+        <v>-1.159</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3627</v>
+        <v>2.531</v>
       </c>
       <c r="G5" t="n">
         <v>1.6231</v>
@@ -844,13 +844,13 @@
         <v>3.9677</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.6255</v>
+        <v>-1.4539</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.5586</v>
+        <v>-0.5554</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0669</v>
+        <v>-0.8985</v>
       </c>
       <c r="V5" t="n">
         <v>1.4012</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1535</v>
+        <v>0.1801</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0155</v>
+        <v>-0.1572</v>
       </c>
       <c r="F6" t="n">
-        <v>0.169</v>
+        <v>0.3374</v>
       </c>
       <c r="G6" t="n">
         <v>0.2128</v>
@@ -922,13 +922,13 @@
         <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5112</v>
+        <v>-0.4846</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0567</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.3996</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1352</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3626</v>
+        <v>-0.0004</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1984</v>
+        <v>-0.8923</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8358</v>
+        <v>0.8919</v>
       </c>
       <c r="G7" t="n">
         <v>0.728</v>
@@ -1000,13 +1000,13 @@
         <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8922</v>
+        <v>-0.53</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2494</v>
+        <v>0.0567</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6428</v>
+        <v>-0.5867</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. DIAZ SANCHEZ</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7251</v>
+        <v>-0.4482</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6126</v>
+        <v>-0.9315</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8875</v>
+        <v>0.4833</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0355</v>
+        <v>-1.3055</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0955</v>
+        <v>0.2065</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.131</v>
+        <v>-1.512</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.3874</v>
       </c>
       <c r="K8" t="n">
-        <v>0.348</v>
+        <v>0.3279</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2801</v>
+        <v>-0.7153</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1035</v>
+        <v>-0.9181</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2525</v>
+        <v>-0.1214</v>
       </c>
       <c r="O8" t="n">
-        <v>0.149</v>
+        <v>-0.7967</v>
       </c>
       <c r="P8" t="n">
         <v>1.3887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1495</v>
+        <v>-0.5314</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7481</v>
+        <v>-0.5441</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4014</v>
+        <v>0.0127</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>R. DIAZ SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9671</v>
+        <v>-0.7914</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1979</v>
+        <v>-1.5105</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2308</v>
+        <v>0.7191</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3055</v>
+        <v>-1.0355</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2065</v>
+        <v>0.0955</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.512</v>
+        <v>-1.131</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3874</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3279</v>
+        <v>0.348</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7153</v>
+        <v>-1.2801</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9181</v>
+        <v>-0.1035</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1214</v>
+        <v>-0.2525</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7967</v>
+        <v>0.149</v>
       </c>
       <c r="P9" t="n">
         <v>1.3887</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0503</v>
+        <v>-1.2158</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8105</v>
+        <v>-0.6461</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2398</v>
+        <v>-0.5697</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4256</v>
+        <v>-1.2051</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3904</v>
+        <v>1.5547</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8159</v>
+        <v>-2.7598</v>
       </c>
       <c r="G10" t="n">
         <v>0.2811</v>
@@ -1234,13 +1234,13 @@
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6824</v>
+        <v>-0.462</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0056</v>
+        <v>0.1588</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6768</v>
+        <v>-0.6207</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4129</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3656</v>
+        <v>-2.3327</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4785</v>
+        <v>-0.5579</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.887</v>
+        <v>-1.7748</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9521</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5486</v>
+        <v>-0.5158</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0056</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.543</v>
+        <v>-0.4308</v>
       </c>
       <c r="V11" t="n">
         <v>1.7384</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7541</v>
+        <v>4.689299999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5507</v>
+        <v>-0.6156000000000009</v>
       </c>
       <c r="F12" t="n">
-        <v>5.305099999999999</v>
+        <v>5.305000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0001</v>
@@ -1366,7 +1366,7 @@
         <v>5.682499999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>2.476500000000001</v>
+        <v>2.4765</v>
       </c>
       <c r="L12" t="n">
         <v>3.205899999999999</v>
@@ -1390,13 +1390,13 @@
         <v>21.8223</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.3118</v>
+        <v>-6.376799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.5499</v>
+        <v>-1.6148</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.7621</v>
+        <v>-4.762</v>
       </c>
       <c r="V12" t="n">
         <v>2.1469</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7568</v>
+        <v>4.8359</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7857</v>
+        <v>3.3979</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9711</v>
+        <v>1.438</v>
       </c>
       <c r="G13" t="n">
         <v>1.8089</v>
@@ -1468,13 +1468,13 @@
         <v>1.9838</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3506</v>
+        <v>1.4298</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0566</v>
+        <v>0.5556</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4072</v>
+        <v>0.8742</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3866</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. BALTÀ CASTELLTORT</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2051</v>
+        <v>0.7489</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4347</v>
+        <v>0.3521</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2295</v>
+        <v>0.3968</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5363</v>
+        <v>0.0403</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2668</v>
+        <v>0.0403</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2695</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1742</v>
+        <v>0.0403</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0537</v>
+        <v>0.0403</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1205</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6379</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7869</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.149</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2474</v>
+        <v>0.3118</v>
       </c>
       <c r="T14" t="n">
-        <v>3.0496</v>
+        <v>0.3118</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1978</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.785</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1947</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.9797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>A. BALTÀ CASTELLTORT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0549</v>
+        <v>-0.2412</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6582</v>
+        <v>0.9042</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3968</v>
+        <v>-1.1454</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0403</v>
+        <v>0.5363</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0403</v>
+        <v>0.2668</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.2695</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0403</v>
+        <v>1.1742</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0403</v>
+        <v>1.0537</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.1205</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0.6379</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.7869</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3968</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6178</v>
+        <v>1.8011</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6178</v>
+        <v>1.5192</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.2819</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.785</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.9797</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1605</v>
+        <v>-0.3994</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2403</v>
+        <v>-0.4363</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4008</v>
+        <v>0.0369</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2114</v>
+        <v>3.3344</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0081</v>
+        <v>2.898</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2034</v>
+        <v>0.4364</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3096</v>
+        <v>3.2151</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0325</v>
+        <v>2.7982</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7229</v>
+        <v>0.4169</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9018</v>
+        <v>0.1193</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0244</v>
+        <v>0.0998</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9263</v>
+        <v>0.0195</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7935</v>
+        <v>-4.3645</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-5.9515</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2574</v>
+        <v>1.1379</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.8277</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2925</v>
+        <v>0.3102</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.5073</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.9797</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. TEJERO CASASAYAS</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6611</v>
+        <v>-0.4372</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6021</v>
+        <v>1.2789</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9409999999999999</v>
+        <v>-1.7161</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1461</v>
+        <v>0.4045</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.764</v>
+        <v>0.8865</v>
       </c>
       <c r="I17" t="n">
-        <v>0.618</v>
+        <v>-0.4819</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4621</v>
+        <v>1.7161</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5917</v>
+        <v>1.6734</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1296</v>
+        <v>0.0427</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.3116</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1723</v>
+        <v>-0.7869</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5117</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P17" t="n">
         <v>-0.3968</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="S17" t="n">
-        <v>0.857</v>
+        <v>-0.1077</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3119</v>
+        <v>0.0227</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5451</v>
+        <v>-0.1304</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0247</v>
+        <v>-0.3373</v>
       </c>
       <c r="W17" t="n">
         <v>0.532</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5073</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. FONS TEIXIDO</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7101</v>
+        <v>-0.5483</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6202</v>
+        <v>-0.3719</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0898</v>
+        <v>-0.1764</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2859</v>
+        <v>-1.2114</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1087</v>
+        <v>-1.0081</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8227</v>
+        <v>-0.2034</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1878</v>
+        <v>-0.3096</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2203</v>
+        <v>-1.0325</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0325</v>
+        <v>0.7229</v>
       </c>
       <c r="M18" t="n">
         <v>-0.9018</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1116</v>
+        <v>0.0244</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7902</v>
+        <v>-0.9263</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3927</v>
+        <v>-0.1304</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1678</v>
+        <v>-0.0623</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2249</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>E. TEJERO CASASAYAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9473</v>
+        <v>-1.0335</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7688</v>
+        <v>-1.8062</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7161</v>
+        <v>0.7726</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4045</v>
+        <v>-1.1461</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8865</v>
+        <v>-1.764</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4819</v>
+        <v>0.618</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7161</v>
+        <v>-0.4621</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6734</v>
+        <v>-1.5917</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0427</v>
+        <v>1.1296</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3116</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7869</v>
+        <v>-0.1723</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5117</v>
       </c>
       <c r="P19" t="n">
         <v>-0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6178</v>
+        <v>0.4846</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4874</v>
+        <v>0.1078</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1304</v>
+        <v>0.3768</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3373</v>
+        <v>0.0247</v>
       </c>
       <c r="W19" t="n">
         <v>0.532</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8692</v>
+        <v>-0.5073</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>C. FONS TEIXIDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8815</v>
+        <v>-1.6564</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7374</v>
+        <v>-1.5385</v>
       </c>
       <c r="F20" t="n">
-        <v>1.856</v>
+        <v>-0.1179</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9317</v>
+        <v>0.2859</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0431</v>
+        <v>1.1087</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1114</v>
+        <v>-0.8227</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9544</v>
+        <v>1.1878</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9167999999999999</v>
+        <v>1.2203</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0376</v>
+        <v>-0.0325</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0228</v>
+        <v>-0.9018</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1263</v>
+        <v>-0.1116</v>
       </c>
       <c r="O20" t="n">
-        <v>0.149</v>
+        <v>-0.7902</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5871</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8786</v>
+        <v>0.4464</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1928</v>
+        <v>0.2495</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6858</v>
+        <v>0.1969</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2413</v>
+        <v>-0.6032</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2413</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1365</v>
+        <v>-1.7794</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8647</v>
+        <v>-3.6354</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2718</v>
+        <v>1.856</v>
       </c>
       <c r="G21" t="n">
-        <v>3.3344</v>
+        <v>-0.9317</v>
       </c>
       <c r="H21" t="n">
-        <v>2.898</v>
+        <v>-1.0431</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4364</v>
+        <v>0.1114</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2151</v>
+        <v>-0.9544</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7982</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4169</v>
+        <v>-0.0376</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1193</v>
+        <v>0.0228</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0998</v>
+        <v>-0.1263</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0195</v>
+        <v>0.149</v>
       </c>
       <c r="P21" t="n">
-        <v>-4.3645</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.9515</v>
+        <v>-2.9758</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5991</v>
+        <v>0.9806</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6008</v>
+        <v>0.2948</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0016</v>
+        <v>0.6858</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5073</v>
+        <v>-0.2413</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9797</v>
+        <v>-0.2413</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2741</v>
+        <v>-3.2436</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3681</v>
+        <v>-3.4499</v>
       </c>
       <c r="F22" t="n">
-        <v>0.094</v>
+        <v>0.2062</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1213</v>
@@ -2170,13 +2170,13 @@
         <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0726</v>
+        <v>0.9579</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0171</v>
+        <v>0.9354</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0897</v>
+        <v>0.0226</v>
       </c>
       <c r="V22" t="n">
         <v>1.689</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7543</v>
+        <v>-3.754200000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3048</v>
+        <v>-5.305099999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5509</v>
+        <v>1.5507</v>
       </c>
       <c r="G23" t="n">
         <v>0.9998</v>
@@ -2221,7 +2221,7 @@
         <v>-1.3929</v>
       </c>
       <c r="J23" t="n">
-        <v>6.682499999999999</v>
+        <v>6.682500000000001</v>
       </c>
       <c r="K23" t="n">
         <v>4.869499999999999</v>
@@ -2248,16 +2248,16 @@
         <v>11.9031</v>
       </c>
       <c r="S23" t="n">
-        <v>7.312000000000001</v>
+        <v>7.311999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>4.762100000000001</v>
+        <v>4.7622</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5498</v>
+        <v>2.5499</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.146999999999999</v>
+        <v>-2.147</v>
       </c>
       <c r="W23" t="n">
         <v>5.0728</v>
